--- a/feedback-reports/Java_Object_Oriented_Programming.xlsx
+++ b/feedback-reports/Java_Object_Oriented_Programming.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34875B87-C48D-4E24-BB55-D1FECAC62B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{34875B87-C48D-4E24-BB55-D1FECAC62B85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{40830C38-E9B7-4EA7-A90A-1971876953DD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{53BC6B5F-F2D8-4FBE-A283-EBF1F5307433}"/>
   </bookViews>
@@ -26,10 +26,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
   <si>
     <t>Program Name:</t>
   </si>
@@ -284,13 +284,16 @@
   </si>
   <si>
     <t>Display Java,VsCode,GitLab</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,16 +306,19 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -438,7 +444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -465,6 +471,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -484,17 +502,8 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -831,18 +840,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567DDD35-0248-4192-9031-AB5EA04CEFE1}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.69921875" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" style="8" customWidth="1"/>
-    <col min="5" max="7" width="29.109375" customWidth="1"/>
-    <col min="8" max="11" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="29.09765625" style="8" customWidth="1"/>
+    <col min="5" max="7" width="29.09765625" customWidth="1"/>
+    <col min="8" max="11" width="8.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="31.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -856,8 +865,9 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.6">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -869,8 +879,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="27.6">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -890,10 +901,13 @@
         <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="27.6">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -912,9 +926,10 @@
       <c r="F4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.4">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -935,7 +950,7 @@
       </c>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -955,7 +970,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -975,7 +990,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -995,7 +1010,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -1015,7 +1030,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -1035,7 +1050,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -1055,7 +1070,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1075,7 +1090,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -1095,7 +1110,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1115,68 +1130,68 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="41.4">
       <c r="A15" s="5">
         <v>12</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+    <row r="16" spans="1:8" ht="27.6">
+      <c r="A16" s="10">
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+    <row r="17" spans="1:6" ht="27.6">
+      <c r="A17" s="10">
         <v>14</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+    <row r="18" spans="1:6" ht="27.6">
+      <c r="A18" s="10">
         <v>15</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1192,9 +1207,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2154ACF6-D455-4A45-805C-CDAF071C70EF}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="345">
       <c r="A1" s="5">
         <v>22</v>
       </c>
@@ -1215,7 +1230,7 @@
       </c>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" ht="207" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="409.6">
       <c r="A2" s="5">
         <v>23</v>
       </c>
@@ -1236,94 +1251,94 @@
       </c>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
+    <row r="3" spans="1:7" ht="43.2">
+      <c r="A3" s="14">
         <v>24</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="14" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="11"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:7" ht="259.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="11"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:7" ht="230.4">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="16"/>
-    </row>
-    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="11"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" ht="230.4">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="11"/>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:7" ht="288">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="11"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:7" ht="201.6">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="12"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" ht="216">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" ht="358.8">
       <c r="A10" s="5">
         <v>25</v>
       </c>
@@ -1344,7 +1359,7 @@
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="193.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="409.6">
       <c r="A11" s="5">
         <v>26</v>
       </c>
@@ -1365,7 +1380,7 @@
       </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="138" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="409.6">
       <c r="A12" s="5">
         <v>27</v>
       </c>
@@ -1386,7 +1401,7 @@
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="207" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="409.6">
       <c r="A13" s="5">
         <v>28</v>
       </c>
@@ -1409,18 +1424,27 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="G3:G9"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="C3:C9"/>
     <mergeCell ref="D3:D9"/>
     <mergeCell ref="E3:E9"/>
-    <mergeCell ref="G3:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008081BF50E816F94B87E854E2907183B0" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6f57204d0cc9b1c65f7ab94eaa7dcc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b8ad293-1655-4b1e-95cd-578b981aff66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed196dee19b1527225c6137bc92e865" ns2:_="">
     <xsd:import namespace="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
@@ -1582,15 +1606,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -1598,6 +1613,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD98D38-FE2A-48E1-B0A3-DCC684CCE6CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268C072E-0EA3-4280-A62A-2E66ACA6841D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1615,26 +1638,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD98D38-FE2A-48E1-B0A3-DCC684CCE6CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0B02991-2B45-40CC-8CD4-349641D3A809}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/feedback-reports/Java_Object_Oriented_Programming.xlsx
+++ b/feedback-reports/Java_Object_Oriented_Programming.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandita.vora\OneDrive - NIIT Limited\NIIT-AI Powered FSE - General\Design Docs\FSE-v6\Feedback-App\feedback-reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niit.sharepoint.com/sites/NIIT-AIPoweredFSE/Shared Documents/General/Design Docs/FSE-v6/Website-Feedback/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{34875B87-C48D-4E24-BB55-D1FECAC62B85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{40830C38-E9B7-4EA7-A90A-1971876953DD}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{34875B87-C48D-4E24-BB55-D1FECAC62B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74E1400F-CBF4-4B29-BBBE-76126C53CB43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{53BC6B5F-F2D8-4FBE-A283-EBF1F5307433}"/>
   </bookViews>
@@ -26,10 +26,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,8 +39,43 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}</author>
+    <author>tc={325600A8-3AE0-4149-A7AA-FC6E14B13328}</author>
+  </authors>
+  <commentList>
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @R Mythreye This is not very clear. Try to break it down into points
+Reply:
+    @Nandita Vora done
+Reply:
+    This is not reflecting the changes we discussed</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="1" shapeId="0" xr:uid="{325600A8-3AE0-4149-A7AA-FC6E14B13328}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @R Mythreye Please check the spellings and case conventions, it should be exactly as per the official site.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>Program Name:</t>
   </si>
@@ -84,106 +119,7 @@
     <t>Tools &amp; Technologies</t>
   </si>
   <si>
-    <t>Missing Tools</t>
-  </si>
-  <si>
-    <t>Listed on page: Java, SQL.</t>
-  </si>
-  <si>
-    <t>The list omits tools and technologies surfaced in the product description: MySQL (database engine), Maven (build tool), JUnit (testing), GenAI Tools (referenced in subqueries sprint).</t>
-  </si>
-  <si>
-    <t>Add: 'MySQL, Maven, JUnit, GenAI Tools like ChatGPT, Gemini'</t>
-  </si>
-  <si>
     <t>Projects You'll Build</t>
-  </si>
-  <si>
-    <t>Capstone Project Card</t>
-  </si>
-  <si>
-    <t>Capstone Project — Develop a functional application using Java that demonstrates core programming concepts and problem-solving skills. The project should incorporate object-oriented programming principles, data handling, and basic database integration to address a real-world scenario.</t>
-  </si>
-  <si>
-    <t>Program has no Capstone Project course in the product description — the description shows 4 courses, each ending with its own Course-End Project. The term 'Capstone' should not appear on the page.</t>
-  </si>
-  <si>
-    <t>Replace 'Capstone Project' with 'Project'. Update the section to surface the four Course-End Projects (one per course) using the Module Activity examples on the page (e.g., Online Bookstore Database for Course 1; Library Management System for Course 2; Data Structure Implementation Project for Course 3; Java Application with Collections, Streams and Functional Programming for Course 4).</t>
-  </si>
-  <si>
-    <t>Course-End Projects</t>
-  </si>
-  <si>
-    <t>Not present on page</t>
-  </si>
-  <si>
-    <t>Each of the four courses has its own Course-End Project in the description's sprint structure (Module Activity items hint at these). The page collapses all four into a single generic 'Capstone Project' card, hiding the per-course portfolio depth.</t>
-  </si>
-  <si>
-    <t>Add six project cards:</t>
-  </si>
-  <si>
-    <t>1. Fitness Tracker Database - Design a fitness tracker database managing workouts, health data, subscriptions, and personalized progress tracking insights.</t>
-  </si>
-  <si>
-    <t>2. Online Bookstore Database — Design and implement a MySQL database with ER modelling, normalization, joins, subqueries and stored procedures.</t>
-  </si>
-  <si>
-    <t>3. Library Management System — Build a Core Java application using OOP principles, inheritance, polymorphism and exception handling.</t>
-  </si>
-  <si>
-    <t>4. Data Structure Implementation Project — Implement and benchmark searching, sorting, linked lists, hashing and BSTs to demonstrate problem-solving with DSA.</t>
-  </si>
-  <si>
-    <t>5. EcoRide – Create a Java ride-sharing simulator with role-based menus for drivers and riders including booking and validation.</t>
-  </si>
-  <si>
-    <t>6. FarmConnect - Build a Java farm supply chain app enabling farmers to list produce and buyers to order and track deliveries.</t>
-  </si>
-  <si>
-    <t>LinkedIn Visibility Callout</t>
-  </si>
-  <si>
-    <t>Boost Your Career Visibility — Showcasing a professional Capstone Project on your LinkedIn increases recruiter interest significantly. Build production-ready work that speaks for itself.</t>
-  </si>
-  <si>
-    <t>Callout uses the term 'Capstone Project' which does not exist as a course in this program; SKILL forbids 'Capstone' on pages where the program has no Capstone course.</t>
-  </si>
-  <si>
-    <t>Replace with: 'Boost Your Career Visibility — Showcasing your professional Course-End Projects on your LinkedIn increases recruiter interest significantly. Build production-ready work that speaks for itself.'</t>
-  </si>
-  <si>
-    <t>Learning Outcomes</t>
-  </si>
-  <si>
-    <t>Coverage vs Description</t>
-  </si>
-  <si>
-    <t>Page outcomes: 1) Design and manage relational databases using SQL... 2) Develop Java applications using core programming concepts... 3) Apply data structures and algorithms... 4) Write optimized and maintainable code using Java Collections, Lambdas, and Stream APIs. 5) Test and validate Java programs using unit testing and debugging techniques. 6) Build structured software solutions...</t>
-  </si>
-  <si>
-    <t>Outcomes are reasonable but generic — they don't surface the description's positioning that learners are prepared for the 'entry-level Java Developer role' nor the description's emphasis on 'professional best practices and the right mindset for success'.</t>
-  </si>
-  <si>
-    <t>Add a closing outcome bullet: 'Be job-ready for the entry-level Java Developer role by combining technical skills with professional best practices and the right engineering mindset.'</t>
-  </si>
-  <si>
-    <t>Prerequisites</t>
-  </si>
-  <si>
-    <t>Description does not specify prerequisites, but the page also lacks a Prerequisites section. Per the page FAQ the program is 'open to learners from all academic backgrounds, and prior coding experience is not mandatory'. This positioning belongs upfront, not buried in the FAQ.</t>
-  </si>
-  <si>
-    <t>Add a Prerequisites block: 'Open to all academic backgrounds — prior coding experience is not mandatory. Class X, XII and graduates are eligible; ambitious undergraduates may also apply.'</t>
-  </si>
-  <si>
-    <t>Why This Program</t>
-  </si>
-  <si>
-    <t>Description's 'Progressively Builds Core Competencies' framing — the four core competencies (RDBMS, Core/OOP Java, DSA, Streams &amp; Lambdas) sequenced to take a learner from databases through to advanced Java — is not surfaced as a 'Why this program' section.</t>
-  </si>
-  <si>
-    <t>Add a 'Why This Program' block: 'This program is built to progressively develop the four core competencies for the entry-level Java Developer role: (1) Designing and querying relational databases with MySQL; (2) Programming with Core and Object-Oriented Java; (3) Applying Data Structures and Algorithms for efficient problem solving; (4) Writing modern Java code with Lambdas, Streams and Collections.'</t>
   </si>
   <si>
     <t>https://beta.niit.com/india/course/java-object-oriented-programming</t>
@@ -211,36 +147,6 @@
     <t>Each sprint is only for 4 hours</t>
   </si>
   <si>
-    <t>1 — Hours</t>
-  </si>
-  <si>
-    <t>2 — Hours</t>
-  </si>
-  <si>
-    <t>3 — Hours</t>
-  </si>
-  <si>
-    <t>4 — Hours</t>
-  </si>
-  <si>
-    <t>5 — Hours</t>
-  </si>
-  <si>
-    <t>6 — Hours</t>
-  </si>
-  <si>
-    <t>7 — Hours</t>
-  </si>
-  <si>
-    <t>8 — Hours</t>
-  </si>
-  <si>
-    <t>9 — Hours</t>
-  </si>
-  <si>
-    <t>10 — Hours</t>
-  </si>
-  <si>
     <t>Weeks 2- 6 hours</t>
   </si>
   <si>
@@ -283,17 +189,42 @@
     <t xml:space="preserve">AI Tools needs to be removed </t>
   </si>
   <si>
-    <t>Display Java,VsCode,GitLab</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>"Add six project cards:
+1. DonateConnect – A Community Donation and Distribution System Connect donors with NGOs to redistribute usable items like clothes, books, and electronics to people in need.
+2. EcoRide – A Simple Ride-Sharing System	Build a ride-sharing system connecting drivers and riders with booking, validation, and capacity management features.
+3. EventEase – Simple Event &amp; Venue Management System	Create an event management system for organizing venues, scheduling events, and enabling attendee discovery and registration.
+4. FarmConnect – A Farmer-to-Market Supply Chain	Design a farmer-to-buyer marketplace for listing, ordering, and tracking fresh produce with inventory management.
+5. GreenPay – A Smart Waste Collection &amp; Reward System	Develop a waste collection platform rewarding citizens with cashback for responsible disposal and sustainable waste management.
+6. PetPal – Adoption Management for Pet Shelters	Build a pet shelter system for listing animals, managing adoption applications, and matching pets with adopters.
+"</t>
+  </si>
+  <si>
+    <t>Replace with Java,VS Code,GitLab</t>
+  </si>
+  <si>
+    <t>Under Curriculum Add:
+"11. Project – Build Solution (Week 3) – 8 Hours
+Apply all skills to build a complete application
+Build and refine a Java application by applying core programming concepts such as logic building, methods, and clean coding practices to create a functional solution.
+ACTIVITY
+Project development using IntelliJ; Version control using Git (commit and push code)
+12. Course-End Assessment (Week 4)- 4 Hours
+Validate knowledge and skills gained
+Assess understanding of core Java concepts and the ability to apply them effectively through structured assessment.
+ACTIVITY
+Concept-based assignments and evaluation
+13. Project Presentation (Week 4)-8Hours
+Showcase the final working application
+Demonstrate the completed project by explaining the logic, approach, and key decisions taken during development.
+ACTIVITY
+Presenting project implementation; Explaining code flow and decisions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,19 +237,16 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -339,6 +267,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -444,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -471,18 +405,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -491,19 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -521,6 +444,84 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{A39C1304-3EE6-4E9A-B4B5-1D2C554E0520}">
+    <Anchor>
+      <Comment id="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-05-04T03:23:36.60" id="{C2858033-5974-45F9-B6F8-1D48B5DD024E}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-05-04T03:23:36.60" id="{B1AE98CA-4F04-4992-94ED-073C6C08AB25}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}"/>
+        </Anchor>
+        <Assign userId="S::R.Mythreye@in.niit.com::f0cdcb60-35d0-41d6-9540-26fc52fcc529" userName="R Mythreye" userProvider="AD"/>
+      </Event>
+      <Event time="2026-05-04T03:23:36.60" id="{A9A73D0A-C194-4D1B-AD54-D392328476BD}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}"/>
+        </Anchor>
+        <SetTitle title="@R Mythreye This is not very clear. Try to break it down into points"/>
+      </Event>
+      <Event time="2026-05-04T04:19:44.72" id="{501E08F6-8A20-48AA-9F47-C546273D7600}">
+        <Attribution userId="S::R.Mythreye@in.niit.com::f0cdcb60-35d0-41d6-9540-26fc52fcc529" userName="R Mythreye" userProvider="AD"/>
+        <Progress percentComplete="100"/>
+      </Event>
+      <Event time="2026-05-04T04:49:26.61" id="{661F1545-674D-4DBC-AD0E-459669BAC282}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Progress percentComplete="0"/>
+      </Event>
+    </History>
+  </Task>
+  <Task id="{538535D4-7993-429A-A5C5-0E687F2B5291}">
+    <Anchor>
+      <Comment id="{325600A8-3AE0-4149-A7AA-FC6E14B13328}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-05-04T04:50:27.17" id="{7F248320-E7FB-4A85-A1FB-8078BD6869A3}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{325600A8-3AE0-4149-A7AA-FC6E14B13328}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-05-04T04:50:27.17" id="{783FD064-D35C-481B-8AD2-6A48175D896A}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{325600A8-3AE0-4149-A7AA-FC6E14B13328}"/>
+        </Anchor>
+        <Assign userId="S::R.Mythreye@in.niit.com::f0cdcb60-35d0-41d6-9540-26fc52fcc529" userName="R Mythreye" userProvider="AD"/>
+      </Event>
+      <Event time="2026-05-04T04:50:27.17" id="{6D13C773-4DC3-4EC8-B5A0-C961E1EE9706}">
+        <Attribution userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" userName="Nandita Vora" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{325600A8-3AE0-4149-A7AA-FC6E14B13328}"/>
+        </Anchor>
+        <SetTitle title="@R Mythreye Please check the spellings and case conventions, it should be exactly as per the official site."/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="R Mythreye" id="{624B8EBD-2B9C-4264-830B-D73B16C2761C}" userId="R.Mythreye@in.niit.com" providerId="PeoplePicker"/>
+  <person displayName="Nandita Vora" id="{2EE441F8-EF20-48ED-9167-45BD4799E06B}" userId="Nandita.Vora@in.niit.com" providerId="PeoplePicker"/>
+  <person displayName="R Mythreye" id="{6E09CCCA-260A-437A-B2FB-401A01197C2C}" userId="S::R.Mythreye@in.niit.com::f0cdcb60-35d0-41d6-9540-26fc52fcc529" providerId="AD"/>
+  <person displayName="Nandita Vora" id="{F20C7023-2444-41D7-B1C0-ED507C1231F7}" userId="S::nandita.vora@in.niit.com::9d3adca1-3a55-4ce0-8cbc-2c4dbd5534b4" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -838,25 +839,53 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F15" dT="2026-05-04T03:23:36.67" personId="{F20C7023-2444-41D7-B1C0-ED507C1231F7}" id="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}">
+    <text>@R Mythreye This is not very clear. Try to break it down into points</text>
+    <mentions>
+      <mention mentionpersonId="{624B8EBD-2B9C-4264-830B-D73B16C2761C}" mentionId="{70C30745-063E-415E-9C6B-A0D2D2355638}" startIndex="0" length="11"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="F15" dT="2026-05-04T04:19:42.89" personId="{6E09CCCA-260A-437A-B2FB-401A01197C2C}" id="{5A24ABA7-D644-4CC1-8847-4D903AAE6C44}" parentId="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}">
+    <text>@Nandita Vora done</text>
+    <mentions>
+      <mention mentionpersonId="{2EE441F8-EF20-48ED-9167-45BD4799E06B}" mentionId="{42E36EE2-032D-42E0-9A39-77595C410DEA}" startIndex="0" length="13"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="F15" dT="2026-05-04T04:49:41.23" personId="{F20C7023-2444-41D7-B1C0-ED507C1231F7}" id="{9BC53AF2-5CE1-46D4-B4BA-BEAD76B01E64}" parentId="{0B5E86D8-33BA-406D-8EEE-3F8F6914C8F6}">
+    <text>This is not reflecting the changes we discussed</text>
+  </threadedComment>
+  <threadedComment ref="F18" dT="2026-05-04T04:50:27.20" personId="{F20C7023-2444-41D7-B1C0-ED507C1231F7}" id="{325600A8-3AE0-4149-A7AA-FC6E14B13328}">
+    <text>@R Mythreye Please check the spellings and case conventions, it should be exactly as per the official site.</text>
+    <mentions>
+      <mention mentionpersonId="{624B8EBD-2B9C-4264-830B-D73B16C2761C}" mentionId="{89A2E03C-7C7C-4472-BEB3-7A6DED5DD5C6}" startIndex="0" length="11"/>
+    </mentions>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567DDD35-0248-4192-9031-AB5EA04CEFE1}">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567DDD35-0248-4192-9031-AB5EA04CEFE1}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.69921875" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.09765625" style="8" customWidth="1"/>
-    <col min="5" max="7" width="29.09765625" customWidth="1"/>
-    <col min="8" max="11" width="8.8984375" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="57.21875" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" customWidth="1"/>
+    <col min="8" max="11" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.2">
+    <row r="1" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -865,23 +894,21 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.6">
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.6">
+    </row>
+    <row r="3" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -901,13 +928,10 @@
         <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27.6">
+    <row r="4" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -918,219 +942,198 @@
         <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" spans="1:8" ht="14.4">
+        <v>19</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="5" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="5" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>63</v>
-      </c>
+      <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="5" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="41.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="372.6" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -1138,10 +1141,14 @@
         <v>12</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="27.6">
+        <v>28</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>13</v>
       </c>
@@ -1149,50 +1156,53 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="27.6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="288" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>14</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="27.6">
+        <v>33</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>15</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1201,225 +1211,135 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{F4423895-BF78-489C-B550-6971731ED614}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2154ACF6-D455-4A45-805C-CDAF071C70EF}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="41.5546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="345">
-      <c r="A1" s="5">
-        <v>22</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>17</v>
-      </c>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" ht="409.6">
-      <c r="A2" s="5">
-        <v>23</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>22</v>
-      </c>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="43.2">
-      <c r="A3" s="14">
-        <v>24</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" ht="259.2">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" ht="230.4">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="20"/>
-    </row>
-    <row r="6" spans="1:7" ht="230.4">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="1:7" ht="288">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20"/>
-    </row>
-    <row r="8" spans="1:7" ht="201.6">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:7" ht="216">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" ht="358.8">
-      <c r="A10" s="5">
-        <v>25</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>36</v>
-      </c>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="15"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="15"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="15"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="409.6">
-      <c r="A11" s="5">
-        <v>26</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>41</v>
-      </c>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="409.6">
-      <c r="A12" s="5">
-        <v>27</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>44</v>
-      </c>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="409.6">
-      <c r="A13" s="5">
-        <v>28</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>47</v>
-      </c>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="6"/>
     </row>
   </sheetData>
@@ -1436,15 +1356,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008081BF50E816F94B87E854E2907183B0" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f6f57204d0cc9b1c65f7ab94eaa7dcc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8b8ad293-1655-4b1e-95cd-578b981aff66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0ed196dee19b1527225c6137bc92e865" ns2:_="">
     <xsd:import namespace="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
@@ -1606,21 +1517,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD98D38-FE2A-48E1-B0A3-DCC684CCE6CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268C072E-0EA3-4280-A62A-2E66ACA6841D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1638,18 +1550,26 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0B02991-2B45-40CC-8CD4-349641D3A809}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="8b8ad293-1655-4b1e-95cd-578b981aff66"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD98D38-FE2A-48E1-B0A3-DCC684CCE6CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>